--- a/Configs/GameConfig/Datas/fg/#IntelKind-情报类型.xlsx
+++ b/Configs/GameConfig/Datas/fg/#IntelKind-情报类型.xlsx
@@ -801,7 +801,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>FG7-ENV-03</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
